--- a/cert-data/Healthcare-Certification-Report-08.10.2026.xlsx
+++ b/cert-data/Healthcare-Certification-Report-08.10.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/Dashboard Reports/Healthcare Dashboard Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{584A364B-29A7-498A-BAF1-0E8D87FCEC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6ED3BF9-5825-4CAF-A387-0EC7C02565FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Certification Report" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="275">
   <si>
     <t>User</t>
   </si>
@@ -101,6 +101,129 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>bryan.davis@KMBS.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Director of Sales</t>
+  </si>
+  <si>
+    <t>FY2026 Direct Sales</t>
+  </si>
+  <si>
+    <t>Mid-Atlantic Sls</t>
+  </si>
+  <si>
+    <t>Vickie</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>VLewis@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Area Vice President</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>EMP_BUS</t>
+  </si>
+  <si>
+    <t>Healthcare Certification for Direct Sales</t>
+  </si>
+  <si>
+    <t>Karie</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Karie.Lee@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Director of Sales - Healthcare</t>
+  </si>
+  <si>
+    <t>Southeast Sls</t>
+  </si>
+  <si>
+    <t>Jeffrey</t>
+  </si>
+  <si>
+    <t>JLee@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Market Vice President- Field Sales</t>
+  </si>
+  <si>
+    <t>Kenneth</t>
+  </si>
+  <si>
+    <t>Scheuer</t>
+  </si>
+  <si>
+    <t>KScheuer@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>BWilson@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Heartland Sls</t>
+  </si>
+  <si>
+    <t>Nicholas</t>
+  </si>
+  <si>
+    <t>Demeduk</t>
+  </si>
+  <si>
+    <t>NDemeduk@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>Slater</t>
+  </si>
+  <si>
+    <t>bslater@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>West Sls</t>
+  </si>
+  <si>
+    <t>Inbo</t>
+  </si>
+  <si>
+    <t>ilee@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Gina</t>
+  </si>
+  <si>
+    <t>Vertullo</t>
+  </si>
+  <si>
+    <t>GVertullo@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Account Executive - Healthcare</t>
+  </si>
+  <si>
     <t>Pamela</t>
   </si>
   <si>
@@ -110,15 +233,6 @@
     <t>PSmock@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Director of Sales</t>
-  </si>
-  <si>
-    <t>FY2026 Direct Sales</t>
-  </si>
-  <si>
-    <t>Heartland Sls</t>
-  </si>
-  <si>
     <t>Michael</t>
   </si>
   <si>
@@ -128,18 +242,6 @@
     <t>MMattson@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Area Vice President</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>EMP_BUS</t>
-  </si>
-  <si>
-    <t>Healthcare Certification for Direct Sales</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -176,9 +278,6 @@
     <t>Dana.Drury@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Market Vice President- Field Sales</t>
-  </si>
-  <si>
     <t>Danielle</t>
   </si>
   <si>
@@ -191,21 +290,6 @@
     <t>Principal Client Relationship Executive - Healthcare</t>
   </si>
   <si>
-    <t>West Sls</t>
-  </si>
-  <si>
-    <t>Bill</t>
-  </si>
-  <si>
-    <t>Slater</t>
-  </si>
-  <si>
-    <t>bslater@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Director of Sales - Healthcare</t>
-  </si>
-  <si>
     <t>Andrea</t>
   </si>
   <si>
@@ -215,18 +299,6 @@
     <t>AAdkins@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Southeast Sls</t>
-  </si>
-  <si>
-    <t>Karie</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Karie.Lee@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Frankie</t>
   </si>
   <si>
@@ -251,27 +323,6 @@
     <t>Senior Account Executive - Healthcare</t>
   </si>
   <si>
-    <t>Bryan</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>bryan.davis@KMBS.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Mid-Atlantic Sls</t>
-  </si>
-  <si>
-    <t>Vickie</t>
-  </si>
-  <si>
-    <t>Lewis</t>
-  </si>
-  <si>
-    <t>VLewis@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Ann</t>
   </si>
   <si>
@@ -338,12 +389,6 @@
     <t>windhamb@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Jeffrey</t>
-  </si>
-  <si>
-    <t>JLee@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Ryan</t>
   </si>
   <si>
@@ -368,33 +413,6 @@
     <t>ADavis@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Kenneth</t>
-  </si>
-  <si>
-    <t>Scheuer</t>
-  </si>
-  <si>
-    <t>KScheuer@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Wilson</t>
-  </si>
-  <si>
-    <t>BWilson@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>Nicholas</t>
-  </si>
-  <si>
-    <t>Demeduk</t>
-  </si>
-  <si>
-    <t>NDemeduk@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Dominic</t>
   </si>
   <si>
@@ -422,9 +440,6 @@
     <t>egoetzke@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Account Executive - Healthcare</t>
-  </si>
-  <si>
     <t>Brian</t>
   </si>
   <si>
@@ -515,12 +530,6 @@
     <t>RDigregorio@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Inbo</t>
-  </si>
-  <si>
-    <t>ilee@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Luis</t>
   </si>
   <si>
@@ -626,15 +635,6 @@
     <t>SSatija@kmbs.konicaminolta.us</t>
   </si>
   <si>
-    <t>Gina</t>
-  </si>
-  <si>
-    <t>Vertullo</t>
-  </si>
-  <si>
-    <t>GVertullo@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
     <t>Ty</t>
   </si>
   <si>
@@ -723,6 +723,144 @@
   </si>
   <si>
     <t>PPompeo@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Hoffmann</t>
+  </si>
+  <si>
+    <t>AHoffmann@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Eldridge</t>
+  </si>
+  <si>
+    <t>Daniel.Eldridge@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Gibbs</t>
+  </si>
+  <si>
+    <t>DGibbs@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Montgomery</t>
+  </si>
+  <si>
+    <t>EMontgomery@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Heath</t>
+  </si>
+  <si>
+    <t>Kidd</t>
+  </si>
+  <si>
+    <t>HKidd@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Chavarria</t>
+  </si>
+  <si>
+    <t>DChavarria@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Gerri</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Gerri.Hadley@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Principal Client Relationship Executive</t>
+  </si>
+  <si>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>jared.jackson@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Senior Business Development Executive</t>
+  </si>
+  <si>
+    <t>Phillip</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>david.pierce@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Keene</t>
+  </si>
+  <si>
+    <t>JKeene@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Steinbrecher</t>
+  </si>
+  <si>
+    <t>jsteinbrecher@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Lisa</t>
+  </si>
+  <si>
+    <t>Donner</t>
+  </si>
+  <si>
+    <t>LDonner@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Logan</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>LSmith@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Venturella</t>
+  </si>
+  <si>
+    <t>RVenturella@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Shayla</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>SMetz@kmbs.konicaminolta.us</t>
+  </si>
+  <si>
+    <t>Travis</t>
+  </si>
+  <si>
+    <t>Sears</t>
+  </si>
+  <si>
+    <t>TSears@kmbs.konicaminolta.us</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1449,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1323,6 +1461,14 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1363,8 +1509,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}" name="Table1" displayName="Table1" ref="A1:T51" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:T51" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}" name="Table1" displayName="Table1" ref="A1:T66" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:T66" xr:uid="{3DB49C0E-B689-40D7-AF80-6540B72913D2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T66">
+    <sortCondition sortBy="cellColor" ref="T1:T66" dxfId="4"/>
+  </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{7E27C642-CD96-4E29-8515-090A1E2597B4}" name="User"/>
     <tableColumn id="21" xr3:uid="{50452B11-87F7-47DB-9B0B-60BC2C16FB02}" name="Active Users" dataDxfId="3"/>
@@ -1710,8 +1859,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB48FCD-FA24-4849-AC79-BFCF63E0FF44}">
-  <dimension ref="A1:U51"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:U66"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -1799,9 +1948,9 @@
       </c>
       <c r="U1"/>
     </row>
-    <row r="2" spans="1:21" ht="15">
+    <row r="2" spans="1:21" ht="16.5">
       <c r="A2">
-        <v>102672</v>
+        <v>111259</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>20</v>
@@ -1843,7 +1992,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="1">
-        <v>39542</v>
+        <v>40330</v>
       </c>
       <c r="P2" t="s">
         <v>32</v>
@@ -1851,88 +2000,100 @@
       <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="10"/>
-      <c r="T2" s="5" t="s">
+      <c r="R2" s="11">
+        <v>46229</v>
+      </c>
+      <c r="S2" s="9" t="str">
+        <f>"FY"&amp;YEAR(R2)-IF(MONTH(R2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2"/>
+    </row>
+    <row r="3" spans="1:21" ht="16.5">
+      <c r="A3">
+        <v>119635</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="U2"/>
-    </row>
-    <row r="3" spans="1:21" ht="15">
-      <c r="A3">
-        <v>103906</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="1">
+        <v>43996</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="11">
+        <v>46224</v>
+      </c>
+      <c r="S3" s="9" t="str">
+        <f>"FY"&amp;YEAR(R3)-IF(MONTH(R3)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R3),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U3"/>
+    </row>
+    <row r="4" spans="1:21" ht="16.5">
+      <c r="A4">
+        <v>123690</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="1">
-        <v>38808</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="10"/>
-      <c r="T3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3"/>
-    </row>
-    <row r="4" spans="1:21" ht="15">
-      <c r="A4">
-        <v>103915</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1944,254 +2105,278 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="1">
+        <v>43844</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="11">
+        <v>46232</v>
+      </c>
+      <c r="S4" s="9" t="str">
+        <f>"FY"&amp;YEAR(R4)-IF(MONTH(R4)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R4),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4"/>
+    </row>
+    <row r="5" spans="1:21" ht="16.5">
+      <c r="A5">
+        <v>124443</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="M4" t="s">
+      <c r="D5" t="s">
         <v>46</v>
       </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="1">
-        <v>36130</v>
-      </c>
-      <c r="P4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" s="10"/>
-      <c r="T4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U4"/>
-    </row>
-    <row r="5" spans="1:21" ht="15">
-      <c r="A5">
-        <v>104738</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
         <v>50</v>
       </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="L5" t="s">
         <v>51</v>
       </c>
-      <c r="I5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="1">
+        <v>44312</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="11">
+        <v>46230</v>
+      </c>
+      <c r="S5" s="9" t="str">
+        <f>"FY"&amp;YEAR(R5)-IF(MONTH(R5)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R5),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5"/>
+    </row>
+    <row r="6" spans="1:21" ht="16.5">
+      <c r="A6">
+        <v>127116</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
+      <c r="D6" t="s">
         <v>53</v>
       </c>
-      <c r="L5" t="s">
+      <c r="E6" t="s">
         <v>54</v>
       </c>
-      <c r="M5" t="s">
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
         <v>55</v>
       </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="1">
-        <v>39335</v>
-      </c>
-      <c r="P5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="10"/>
-      <c r="T5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U5"/>
-    </row>
-    <row r="6" spans="1:21" ht="15">
-      <c r="A6">
-        <v>105722</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
         <v>56</v>
       </c>
-      <c r="D6" t="s">
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
         <v>57</v>
       </c>
-      <c r="E6" t="s">
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="1">
+        <v>45231</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" s="11">
+        <v>46218</v>
+      </c>
+      <c r="S6" s="9" t="str">
+        <f>"FY"&amp;YEAR(R6)-IF(MONTH(R6)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R6),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U6"/>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7">
+        <v>129182</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>58</v>
       </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="I6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="E7" t="s">
         <v>60</v>
       </c>
-      <c r="K6" t="s">
+      <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="L6" t="s">
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="1">
+        <v>45999</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" s="11">
+        <v>46241</v>
+      </c>
+      <c r="S7" s="2" t="str">
+        <f>"FY"&amp;YEAR(R7)-IF(MONTH(R7)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R7),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q2</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U7"/>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8">
+        <v>102672</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>62</v>
       </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="1">
-        <v>34169</v>
-      </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" s="10"/>
-      <c r="T6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6"/>
-    </row>
-    <row r="7" spans="1:21" ht="15">
-      <c r="A7">
-        <v>106003</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
         <v>63</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
         <v>65</v>
       </c>
-      <c r="F7" t="s">
+      <c r="K8" t="s">
         <v>66</v>
       </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="1">
-        <v>37967</v>
-      </c>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" s="10"/>
-      <c r="T7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U7"/>
-    </row>
-    <row r="8" spans="1:21" ht="15">
-      <c r="A8">
-        <v>106138</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="L8" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" t="s">
-        <v>62</v>
-      </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N8" t="s">
         <v>31</v>
       </c>
       <c r="O8" s="1">
-        <v>35492</v>
+        <v>39542</v>
       </c>
       <c r="P8" t="s">
         <v>32</v>
@@ -2201,119 +2386,113 @@
       </c>
       <c r="R8" s="10"/>
       <c r="T8" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U8"/>
     </row>
-    <row r="9" spans="1:21" ht="16.5">
+    <row r="9" spans="1:21">
       <c r="A9">
-        <v>111259</v>
+        <v>103906</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>72</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
         <v>73</v>
       </c>
-      <c r="F9" t="s">
+      <c r="I9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="1">
+        <v>38808</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="10"/>
+      <c r="T9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U9"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10">
+        <v>103915</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" t="s">
         <v>77</v>
       </c>
-      <c r="M9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="1">
-        <v>40330</v>
-      </c>
-      <c r="P9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" s="11">
-        <v>46229</v>
-      </c>
-      <c r="S9" s="9" t="str">
-        <f>"FY"&amp;YEAR(R9)-IF(MONTH(R9)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R9),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="U9"/>
-    </row>
-    <row r="10" spans="1:21" ht="15">
-      <c r="A10">
-        <v>113193</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="K10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" t="s">
+      <c r="L10" t="s">
         <v>79</v>
       </c>
-      <c r="E10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" t="s">
-        <v>29</v>
-      </c>
       <c r="M10" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="N10" t="s">
         <v>31</v>
       </c>
       <c r="O10" s="1">
-        <v>36528</v>
+        <v>36130</v>
       </c>
       <c r="P10" t="s">
         <v>32</v>
@@ -2323,55 +2502,55 @@
       </c>
       <c r="R10" s="10"/>
       <c r="T10" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U10"/>
     </row>
-    <row r="11" spans="1:21" ht="15">
+    <row r="11" spans="1:21">
       <c r="A11">
-        <v>115144</v>
+        <v>104738</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>82</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>83</v>
       </c>
-      <c r="F11" t="s">
-        <v>84</v>
-      </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="K11" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N11" t="s">
         <v>31</v>
       </c>
       <c r="O11" s="1">
-        <v>41362</v>
+        <v>39335</v>
       </c>
       <c r="P11" t="s">
         <v>32</v>
@@ -2381,55 +2560,55 @@
       </c>
       <c r="R11" s="10"/>
       <c r="T11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U11"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12">
+        <v>105722</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" t="s">
         <v>34</v>
       </c>
-      <c r="U11"/>
-    </row>
-    <row r="12" spans="1:21" ht="15">
-      <c r="A12">
-        <v>115424</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" t="s">
-        <v>88</v>
-      </c>
       <c r="K12" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="L12" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N12" t="s">
         <v>31</v>
       </c>
       <c r="O12" s="1">
-        <v>41456</v>
+        <v>34169</v>
       </c>
       <c r="P12" t="s">
         <v>32</v>
@@ -2439,55 +2618,55 @@
       </c>
       <c r="R12" s="10"/>
       <c r="T12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U12"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13">
+        <v>106003</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
         <v>34</v>
       </c>
-      <c r="U12"/>
-    </row>
-    <row r="13" spans="1:21" ht="15">
-      <c r="A13">
-        <v>117563</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" t="s">
-        <v>94</v>
-      </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N13" t="s">
         <v>31</v>
       </c>
       <c r="O13" s="1">
-        <v>42100</v>
+        <v>37967</v>
       </c>
       <c r="P13" t="s">
         <v>32</v>
@@ -2497,55 +2676,55 @@
       </c>
       <c r="R13" s="10"/>
       <c r="T13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14">
+        <v>106138</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" t="s">
         <v>34</v>
       </c>
-      <c r="U13"/>
-    </row>
-    <row r="14" spans="1:21" ht="15">
-      <c r="A14">
-        <v>118764</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" t="s">
-        <v>97</v>
-      </c>
       <c r="K14" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="L14" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N14" t="s">
         <v>31</v>
       </c>
       <c r="O14" s="1">
-        <v>42317</v>
+        <v>35492</v>
       </c>
       <c r="P14" t="s">
         <v>32</v>
@@ -2555,110 +2734,104 @@
       </c>
       <c r="R14" s="10"/>
       <c r="T14" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U14"/>
     </row>
-    <row r="15" spans="1:21" ht="16.5">
+    <row r="15" spans="1:21">
       <c r="A15">
-        <v>119635</v>
-      </c>
-      <c r="B15" s="7" t="s">
+        <v>113193</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="J15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="1">
+        <v>36528</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" s="10"/>
+      <c r="T15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U15"/>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16">
+        <v>115144</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
         <v>100</v>
       </c>
-      <c r="K15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="F16" t="s">
         <v>101</v>
       </c>
-      <c r="M15" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" s="1">
-        <v>43996</v>
-      </c>
-      <c r="P15" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="11">
-        <v>46224</v>
-      </c>
-      <c r="S15" s="9" t="str">
-        <f>"FY"&amp;YEAR(R15)-IF(MONTH(R15)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R15),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="U15"/>
-    </row>
-    <row r="16" spans="1:21" ht="15">
-      <c r="A16">
-        <v>120343</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" t="s">
-        <v>84</v>
-      </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="L16" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="M16" t="s">
         <v>30</v>
@@ -2667,7 +2840,7 @@
         <v>31</v>
       </c>
       <c r="O16" s="1">
-        <v>42821</v>
+        <v>41362</v>
       </c>
       <c r="P16" t="s">
         <v>32</v>
@@ -2677,55 +2850,55 @@
       </c>
       <c r="R16" s="10"/>
       <c r="T16" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U16"/>
     </row>
-    <row r="17" spans="1:21" ht="15">
+    <row r="17" spans="1:21">
       <c r="A17">
-        <v>121515</v>
+        <v>115424</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" t="s">
+        <v>107</v>
+      </c>
+      <c r="M17" t="s">
         <v>24</v>
       </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" t="s">
-        <v>29</v>
-      </c>
-      <c r="M17" t="s">
-        <v>30</v>
-      </c>
       <c r="N17" t="s">
         <v>31</v>
       </c>
       <c r="O17" s="1">
-        <v>43241</v>
+        <v>41456</v>
       </c>
       <c r="P17" t="s">
         <v>32</v>
@@ -2735,55 +2908,55 @@
       </c>
       <c r="R17" s="10"/>
       <c r="T17" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U17"/>
     </row>
-    <row r="18" spans="1:21" ht="15">
+    <row r="18" spans="1:21">
       <c r="A18">
-        <v>122812</v>
+        <v>117563</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="N18" t="s">
         <v>31</v>
       </c>
       <c r="O18" s="1">
-        <v>43557</v>
+        <v>42100</v>
       </c>
       <c r="P18" t="s">
         <v>32</v>
@@ -2793,55 +2966,55 @@
       </c>
       <c r="R18" s="10"/>
       <c r="T18" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U18"/>
     </row>
-    <row r="19" spans="1:21" ht="15">
+    <row r="19" spans="1:21">
       <c r="A19">
-        <v>123471</v>
+        <v>118764</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="K19" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N19" t="s">
         <v>31</v>
       </c>
       <c r="O19" s="1">
-        <v>43753</v>
+        <v>42317</v>
       </c>
       <c r="P19" t="s">
         <v>32</v>
@@ -2851,46 +3024,46 @@
       </c>
       <c r="R19" s="10"/>
       <c r="T19" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U19"/>
     </row>
-    <row r="20" spans="1:21" ht="16.5">
+    <row r="20" spans="1:21">
       <c r="A20">
-        <v>123690</v>
+        <v>120343</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I20" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J20" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K20" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="M20" t="s">
         <v>30</v>
@@ -2899,7 +3072,7 @@
         <v>31</v>
       </c>
       <c r="O20" s="1">
-        <v>43844</v>
+        <v>42821</v>
       </c>
       <c r="P20" t="s">
         <v>32</v>
@@ -2907,33 +3080,27 @@
       <c r="Q20" t="s">
         <v>33</v>
       </c>
-      <c r="R20" s="11">
-        <v>46232</v>
-      </c>
-      <c r="S20" s="9" t="str">
-        <f>"FY"&amp;YEAR(R20)-IF(MONTH(R20)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R20),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T20" s="8" t="s">
-        <v>20</v>
+      <c r="R20" s="10"/>
+      <c r="T20" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="U20"/>
     </row>
-    <row r="21" spans="1:21" ht="16.5">
+    <row r="21" spans="1:21">
       <c r="A21">
-        <v>124443</v>
+        <v>121515</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
         <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>115</v>
       </c>
       <c r="F21" t="s">
         <v>24</v>
@@ -2942,19 +3109,19 @@
         <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="K21" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="L21" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="M21" t="s">
         <v>30</v>
@@ -2963,7 +3130,7 @@
         <v>31</v>
       </c>
       <c r="O21" s="1">
-        <v>44312</v>
+        <v>43241</v>
       </c>
       <c r="P21" t="s">
         <v>32</v>
@@ -2971,63 +3138,57 @@
       <c r="Q21" t="s">
         <v>33</v>
       </c>
-      <c r="R21" s="11">
-        <v>46230</v>
-      </c>
-      <c r="S21" s="9" t="str">
-        <f>"FY"&amp;YEAR(R21)-IF(MONTH(R21)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R21),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>20</v>
+      <c r="R21" s="10"/>
+      <c r="T21" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="U21"/>
     </row>
-    <row r="22" spans="1:21" ht="15">
+    <row r="22" spans="1:21">
       <c r="A22">
-        <v>124636</v>
+        <v>122812</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="L22" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N22" t="s">
         <v>31</v>
       </c>
       <c r="O22" s="1">
-        <v>44396</v>
+        <v>43557</v>
       </c>
       <c r="P22" t="s">
         <v>32</v>
@@ -3037,55 +3198,55 @@
       </c>
       <c r="R22" s="10"/>
       <c r="T22" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U22"/>
     </row>
-    <row r="23" spans="1:21" ht="15">
+    <row r="23" spans="1:21">
       <c r="A23">
-        <v>125310</v>
+        <v>123471</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
         <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="J23" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="K23" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M23" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N23" t="s">
         <v>31</v>
       </c>
       <c r="O23" s="1">
-        <v>44627</v>
+        <v>43753</v>
       </c>
       <c r="P23" t="s">
         <v>32</v>
@@ -3095,15 +3256,15 @@
       </c>
       <c r="R23" s="10"/>
       <c r="T23" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U23"/>
     </row>
-    <row r="24" spans="1:21" ht="15">
+    <row r="24" spans="1:21">
       <c r="A24">
-        <v>125940</v>
-      </c>
-      <c r="B24" s="6" t="s">
+        <v>124636</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C24" t="s">
@@ -3116,34 +3277,34 @@
         <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J24" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="K24" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="M24" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="N24" t="s">
         <v>31</v>
       </c>
       <c r="O24" s="1">
-        <v>44825</v>
+        <v>44396</v>
       </c>
       <c r="P24" t="s">
         <v>32</v>
@@ -3153,55 +3314,55 @@
       </c>
       <c r="R24" s="10"/>
       <c r="T24" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U24"/>
     </row>
-    <row r="25" spans="1:21" ht="15">
+    <row r="25" spans="1:21">
       <c r="A25">
-        <v>126110</v>
+        <v>125310</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J25" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="K25" t="s">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="L25" t="s">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="M25" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N25" t="s">
         <v>31</v>
       </c>
       <c r="O25" s="1">
-        <v>44900</v>
+        <v>44627</v>
       </c>
       <c r="P25" t="s">
         <v>32</v>
@@ -3211,55 +3372,55 @@
       </c>
       <c r="R25" s="10"/>
       <c r="T25" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U25"/>
     </row>
-    <row r="26" spans="1:21" ht="15">
+    <row r="26" spans="1:21">
       <c r="A26">
-        <v>126128</v>
-      </c>
-      <c r="B26" s="7" t="s">
+        <v>125940</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" t="s">
+        <v>134</v>
+      </c>
+      <c r="K26" t="s">
+        <v>135</v>
+      </c>
+      <c r="L26" t="s">
         <v>136</v>
       </c>
-      <c r="D26" t="s">
+      <c r="M26" t="s">
         <v>137</v>
       </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" t="s">
-        <v>139</v>
-      </c>
-      <c r="K26" t="s">
-        <v>140</v>
-      </c>
-      <c r="L26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M26" t="s">
-        <v>30</v>
-      </c>
       <c r="N26" t="s">
         <v>31</v>
       </c>
       <c r="O26" s="1">
-        <v>44907</v>
+        <v>44825</v>
       </c>
       <c r="P26" t="s">
         <v>32</v>
@@ -3269,114 +3430,113 @@
       </c>
       <c r="R26" s="10"/>
       <c r="T26" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U26"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5">
+    <row r="27" spans="1:21">
       <c r="A27">
-        <v>126536</v>
+        <v>126110</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" t="s">
         <v>142</v>
       </c>
-      <c r="D27" t="s">
+      <c r="L27" t="s">
         <v>143</v>
       </c>
-      <c r="E27" t="s">
+      <c r="M27" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" s="1">
+        <v>44900</v>
+      </c>
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>33</v>
+      </c>
+      <c r="R27" s="10"/>
+      <c r="T27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U27"/>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28">
+        <v>126128</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s">
         <v>144</v>
       </c>
-      <c r="F27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" t="s">
-        <v>59</v>
-      </c>
-      <c r="I27" t="s">
-        <v>59</v>
-      </c>
-      <c r="J27" t="s">
-        <v>60</v>
-      </c>
-      <c r="K27" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" t="s">
-        <v>62</v>
-      </c>
-      <c r="M27" t="s">
-        <v>55</v>
-      </c>
-      <c r="N27" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="1">
-        <v>45035</v>
-      </c>
-      <c r="P27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" s="11"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U27"/>
-    </row>
-    <row r="28" spans="1:21" ht="15">
-      <c r="A28">
-        <v>126595</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="K28" t="s">
         <v>145</v>
       </c>
-      <c r="D28" t="s">
+      <c r="L28" t="s">
         <v>146</v>
       </c>
-      <c r="E28" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" t="s">
-        <v>148</v>
-      </c>
-      <c r="G28" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" t="s">
-        <v>39</v>
-      </c>
-      <c r="I28" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L28" t="s">
-        <v>90</v>
-      </c>
       <c r="M28" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N28" t="s">
         <v>31</v>
       </c>
       <c r="O28" s="1">
-        <v>45069</v>
+        <v>44907</v>
       </c>
       <c r="P28" t="s">
         <v>32</v>
@@ -3386,113 +3546,114 @@
       </c>
       <c r="R28" s="10"/>
       <c r="T28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U28"/>
+    </row>
+    <row r="29" spans="1:21" ht="16.5">
+      <c r="A29">
+        <v>126536</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" t="s">
         <v>34</v>
       </c>
-      <c r="U28"/>
-    </row>
-    <row r="29" spans="1:21" ht="15">
-      <c r="A29">
-        <v>126783</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="K29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" t="s">
+        <v>36</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O29" s="1">
+        <v>45035</v>
+      </c>
+      <c r="P29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>33</v>
+      </c>
+      <c r="R29" s="11"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U29"/>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30">
+        <v>126595</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
         <v>150</v>
       </c>
-      <c r="E29" t="s">
+      <c r="D30" t="s">
         <v>151</v>
       </c>
-      <c r="F29" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" t="s">
-        <v>28</v>
-      </c>
-      <c r="L29" t="s">
-        <v>29</v>
-      </c>
-      <c r="M29" t="s">
-        <v>30</v>
-      </c>
-      <c r="N29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O29" s="1">
-        <v>45117</v>
-      </c>
-      <c r="P29" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" s="10"/>
-      <c r="T29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U29"/>
-    </row>
-    <row r="30" spans="1:21" ht="15">
-      <c r="A30">
-        <v>126904</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="E30" t="s">
         <v>152</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>153</v>
       </c>
-      <c r="E30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F30" t="s">
-        <v>70</v>
-      </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="K30" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="N30" t="s">
         <v>31</v>
       </c>
       <c r="O30" s="1">
-        <v>45159</v>
+        <v>45069</v>
       </c>
       <c r="P30" t="s">
         <v>32</v>
@@ -3502,46 +3663,46 @@
       </c>
       <c r="R30" s="10"/>
       <c r="T30" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U30"/>
     </row>
-    <row r="31" spans="1:21" ht="16.5">
+    <row r="31" spans="1:21">
       <c r="A31">
-        <v>127116</v>
+        <v>126783</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J31" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="K31" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L31" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="M31" t="s">
         <v>30</v>
@@ -3550,7 +3711,7 @@
         <v>31</v>
       </c>
       <c r="O31" s="1">
-        <v>45231</v>
+        <v>45117</v>
       </c>
       <c r="P31" t="s">
         <v>32</v>
@@ -3558,80 +3719,73 @@
       <c r="Q31" t="s">
         <v>33</v>
       </c>
-      <c r="R31" s="11">
-        <v>46218</v>
-      </c>
-      <c r="S31" s="9" t="str">
-        <f>"FY"&amp;YEAR(R31)-IF(MONTH(R31)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R31),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T31" s="8" t="s">
-        <v>20</v>
+      <c r="R31" s="10"/>
+      <c r="T31" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="U31"/>
     </row>
-    <row r="32" spans="1:21" ht="16.5">
+    <row r="32" spans="1:21">
       <c r="A32">
+        <v>126904</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32" t="s">
+        <v>160</v>
+      </c>
+      <c r="J32" t="s">
+        <v>161</v>
+      </c>
+      <c r="K32" t="s">
+        <v>162</v>
+      </c>
+      <c r="L32" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>31</v>
+      </c>
+      <c r="O32" s="1">
+        <v>45159</v>
+      </c>
+      <c r="P32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32" s="10"/>
+      <c r="T32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U32"/>
+    </row>
+    <row r="33" spans="1:21" ht="16.5">
+      <c r="A33">
         <v>127239</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" t="s">
-        <v>163</v>
-      </c>
-      <c r="F32" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" t="s">
-        <v>52</v>
-      </c>
-      <c r="K32" t="s">
-        <v>53</v>
-      </c>
-      <c r="L32" t="s">
-        <v>54</v>
-      </c>
-      <c r="M32" t="s">
-        <v>55</v>
-      </c>
-      <c r="N32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O32" s="1">
-        <v>45278</v>
-      </c>
-      <c r="P32" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>33</v>
-      </c>
-      <c r="R32" s="11"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U32"/>
-    </row>
-    <row r="33" spans="1:21" ht="15">
-      <c r="A33">
-        <v>127473</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>20</v>
@@ -3646,34 +3800,34 @@
         <v>166</v>
       </c>
       <c r="F33" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="G33" t="s">
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="I33" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="J33" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="K33" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="L33" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="M33" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="N33" t="s">
         <v>31</v>
       </c>
       <c r="O33" s="1">
-        <v>45393</v>
+        <v>45278</v>
       </c>
       <c r="P33" t="s">
         <v>32</v>
@@ -3681,17 +3835,18 @@
       <c r="Q33" t="s">
         <v>33</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="9"/>
       <c r="T33" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U33"/>
     </row>
-    <row r="34" spans="1:21" ht="15">
+    <row r="34" spans="1:21">
       <c r="A34">
-        <v>127826</v>
-      </c>
-      <c r="B34" s="7" t="s">
+        <v>127473</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C34" t="s">
@@ -3704,34 +3859,34 @@
         <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I34" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="K34" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="N34" t="s">
         <v>31</v>
       </c>
       <c r="O34" s="1">
-        <v>45481</v>
+        <v>45393</v>
       </c>
       <c r="P34" t="s">
         <v>32</v>
@@ -3741,13 +3896,13 @@
       </c>
       <c r="R34" s="10"/>
       <c r="T34" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U34"/>
     </row>
-    <row r="35" spans="1:21" ht="15">
+    <row r="35" spans="1:21">
       <c r="A35">
-        <v>128013</v>
+        <v>127826</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>20</v>
@@ -3762,34 +3917,34 @@
         <v>172</v>
       </c>
       <c r="F35" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I35" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="L35" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="M35" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N35" t="s">
         <v>31</v>
       </c>
       <c r="O35" s="1">
-        <v>45544</v>
+        <v>45481</v>
       </c>
       <c r="P35" t="s">
         <v>32</v>
@@ -3799,55 +3954,55 @@
       </c>
       <c r="R35" s="10"/>
       <c r="T35" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U35"/>
     </row>
-    <row r="36" spans="1:21" ht="15">
+    <row r="36" spans="1:21">
       <c r="A36">
-        <v>128192</v>
+        <v>128013</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K36" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L36" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M36" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N36" t="s">
         <v>31</v>
       </c>
       <c r="O36" s="1">
-        <v>45607</v>
+        <v>45544</v>
       </c>
       <c r="P36" t="s">
         <v>32</v>
@@ -3857,19 +4012,19 @@
       </c>
       <c r="R36" s="10"/>
       <c r="T36" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U36"/>
     </row>
-    <row r="37" spans="1:21" ht="15">
+    <row r="37" spans="1:21">
       <c r="A37">
-        <v>128291</v>
+        <v>128192</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -3878,34 +4033,34 @@
         <v>177</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="J37" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="K37" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="L37" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="M37" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N37" t="s">
         <v>31</v>
       </c>
       <c r="O37" s="1">
-        <v>45628</v>
+        <v>45607</v>
       </c>
       <c r="P37" t="s">
         <v>32</v>
@@ -3915,13 +4070,13 @@
       </c>
       <c r="R37" s="10"/>
       <c r="T37" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U37"/>
     </row>
-    <row r="38" spans="1:21" ht="15">
+    <row r="38" spans="1:21">
       <c r="A38">
-        <v>128321</v>
+        <v>128291</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>20</v>
@@ -3936,34 +4091,34 @@
         <v>180</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I38" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J38" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="K38" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="M38" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="N38" t="s">
         <v>31</v>
       </c>
       <c r="O38" s="1">
-        <v>45664</v>
+        <v>45628</v>
       </c>
       <c r="P38" t="s">
         <v>32</v>
@@ -3973,19 +4128,19 @@
       </c>
       <c r="R38" s="10"/>
       <c r="T38" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="U38"/>
     </row>
-    <row r="39" spans="1:21" ht="15">
+    <row r="39" spans="1:21">
       <c r="A39">
-        <v>128757</v>
+        <v>128321</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
         <v>182</v>
@@ -3994,34 +4149,34 @@
         <v>183</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="K39" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="L39" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="M39" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N39" t="s">
         <v>31</v>
       </c>
       <c r="O39" s="1">
-        <v>45796</v>
+        <v>45664</v>
       </c>
       <c r="P39" t="s">
         <v>32</v>
@@ -4031,18 +4186,18 @@
       </c>
       <c r="R39" s="10"/>
       <c r="T39" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40">
-        <v>128969</v>
+        <v>128757</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
         <v>185</v>
@@ -4051,34 +4206,34 @@
         <v>186</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="I40" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="K40" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="L40" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N40" t="s">
         <v>31</v>
       </c>
       <c r="O40" s="1">
-        <v>45922</v>
+        <v>45796</v>
       </c>
       <c r="P40" t="s">
         <v>32</v>
@@ -4088,12 +4243,12 @@
       </c>
       <c r="R40" s="10"/>
       <c r="T40" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41">
-        <v>129148</v>
+        <v>128969</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>20</v>
@@ -4108,34 +4263,34 @@
         <v>189</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="J41" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="K41" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="L41" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="M41" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N41" t="s">
         <v>31</v>
       </c>
       <c r="O41" s="1">
-        <v>45999</v>
+        <v>45922</v>
       </c>
       <c r="P41" t="s">
         <v>32</v>
@@ -4145,54 +4300,54 @@
       </c>
       <c r="R41" s="10"/>
       <c r="T41" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42">
-        <v>129153</v>
-      </c>
-      <c r="B42" s="6" t="s">
+        <v>129148</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" t="s">
+        <v>192</v>
+      </c>
+      <c r="F42" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" t="s">
         <v>193</v>
       </c>
-      <c r="D42" t="s">
+      <c r="K42" t="s">
         <v>194</v>
       </c>
-      <c r="E42" t="s">
+      <c r="L42" t="s">
         <v>195</v>
       </c>
-      <c r="F42" t="s">
-        <v>128</v>
-      </c>
-      <c r="G42" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" t="s">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s">
-        <v>129</v>
-      </c>
-      <c r="K42" t="s">
-        <v>130</v>
-      </c>
-      <c r="L42" t="s">
-        <v>131</v>
-      </c>
       <c r="M42" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="N42" t="s">
         <v>31</v>
       </c>
       <c r="O42" s="1">
-        <v>46006</v>
+        <v>45999</v>
       </c>
       <c r="P42" t="s">
         <v>32</v>
@@ -4202,12 +4357,12 @@
       </c>
       <c r="R42" s="10"/>
       <c r="T42" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43">
-        <v>129182</v>
+        <v>129153</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>20</v>
@@ -4222,34 +4377,34 @@
         <v>198</v>
       </c>
       <c r="F43" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
       </c>
       <c r="H43" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I43" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="K43" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="M43" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="N43" t="s">
         <v>31</v>
       </c>
       <c r="O43" s="1">
-        <v>45999</v>
+        <v>46006</v>
       </c>
       <c r="P43" t="s">
         <v>32</v>
@@ -4257,15 +4412,9 @@
       <c r="Q43" t="s">
         <v>33</v>
       </c>
-      <c r="R43" s="11">
-        <v>46241</v>
-      </c>
-      <c r="S43" s="2" t="str">
-        <f>"FY"&amp;YEAR(R43)-IF(MONTH(R43)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R43),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q2</v>
-      </c>
-      <c r="T43" s="8" t="s">
-        <v>20</v>
+      <c r="R43" s="10"/>
+      <c r="T43" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4285,25 +4434,25 @@
         <v>201</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="J44" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M44" t="s">
         <v>24</v>
@@ -4322,10 +4471,10 @@
       </c>
       <c r="R44" s="10"/>
       <c r="T44" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45">
         <v>129377</v>
       </c>
@@ -4342,28 +4491,28 @@
         <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="I45" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K45" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="N45" t="s">
         <v>31</v>
@@ -4379,10 +4528,10 @@
       </c>
       <c r="R45" s="10"/>
       <c r="T45" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46">
         <v>129427</v>
       </c>
@@ -4390,25 +4539,25 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I46" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J46" t="s">
         <v>205</v>
@@ -4436,10 +4585,10 @@
       </c>
       <c r="R46" s="10"/>
       <c r="T46" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47">
         <v>127835</v>
       </c>
@@ -4462,10 +4611,10 @@
         <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s">
         <v>212</v>
@@ -4493,10 +4642,10 @@
       </c>
       <c r="R47" s="10"/>
       <c r="T47" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48">
         <v>129610</v>
       </c>
@@ -4513,28 +4662,28 @@
         <v>216</v>
       </c>
       <c r="F48" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
       </c>
       <c r="H48" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I48" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J48" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K48" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="M48" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N48" t="s">
         <v>31</v>
@@ -4550,10 +4699,10 @@
       </c>
       <c r="R48" s="10"/>
       <c r="T48" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49">
         <v>129570</v>
       </c>
@@ -4576,10 +4725,10 @@
         <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s">
         <v>220</v>
@@ -4607,10 +4756,10 @@
       </c>
       <c r="R49" s="10"/>
       <c r="T49" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50">
         <v>129619</v>
       </c>
@@ -4627,28 +4776,28 @@
         <v>225</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I50" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="J50" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K50" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="L50" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="M50" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N50" t="s">
         <v>31</v>
@@ -4664,10 +4813,10 @@
       </c>
       <c r="R50" s="10"/>
       <c r="T50" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" ht="15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51">
         <v>129628</v>
       </c>
@@ -4684,28 +4833,28 @@
         <v>228</v>
       </c>
       <c r="F51" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I51" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J51" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K51" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L51" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="M51" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N51" t="s">
         <v>31</v>
@@ -4721,13 +4870,868 @@
       </c>
       <c r="R51" s="10"/>
       <c r="T51" s="5" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52">
+        <v>122614</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" t="s">
+        <v>229</v>
+      </c>
+      <c r="E52" t="s">
+        <v>230</v>
+      </c>
+      <c r="F52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>73</v>
+      </c>
+      <c r="I52" t="s">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s">
+        <v>231</v>
+      </c>
+      <c r="K52" t="s">
+        <v>232</v>
+      </c>
+      <c r="L52" t="s">
+        <v>233</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
+        <v>31</v>
+      </c>
+      <c r="O52" s="1">
+        <v>43528</v>
+      </c>
+      <c r="P52" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>33</v>
+      </c>
+      <c r="R52" s="10"/>
+      <c r="T52" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53">
+        <v>129105</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" t="s">
+        <v>234</v>
+      </c>
+      <c r="D53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" t="s">
+        <v>236</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" t="s">
+        <v>73</v>
+      </c>
+      <c r="J53" t="s">
+        <v>237</v>
+      </c>
+      <c r="K53" t="s">
+        <v>238</v>
+      </c>
+      <c r="L53" t="s">
+        <v>239</v>
+      </c>
+      <c r="M53" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" t="s">
+        <v>31</v>
+      </c>
+      <c r="O53" s="1">
+        <v>45985</v>
+      </c>
+      <c r="P53" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>33</v>
+      </c>
+      <c r="R53" s="10"/>
+      <c r="T53" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54">
+        <v>111249</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" t="s">
+        <v>214</v>
+      </c>
+      <c r="F54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
+        <v>25</v>
+      </c>
+      <c r="H54" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" t="s">
+        <v>73</v>
+      </c>
+      <c r="J54" t="s">
+        <v>240</v>
+      </c>
+      <c r="K54" t="s">
+        <v>241</v>
+      </c>
+      <c r="L54" t="s">
+        <v>242</v>
+      </c>
+      <c r="M54" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" s="1">
+        <v>40336</v>
+      </c>
+      <c r="P54" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>33</v>
+      </c>
+      <c r="R54" s="10"/>
+      <c r="T54" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55">
+        <v>128348</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>231</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" t="s">
+        <v>212</v>
+      </c>
+      <c r="K55" t="s">
+        <v>213</v>
+      </c>
+      <c r="L55" t="s">
+        <v>214</v>
+      </c>
+      <c r="M55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" t="s">
+        <v>31</v>
+      </c>
+      <c r="O55" s="1">
+        <v>45642</v>
+      </c>
+      <c r="P55" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>33</v>
+      </c>
+      <c r="R55" s="10"/>
+      <c r="T55" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56">
+        <v>103908</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>231</v>
+      </c>
+      <c r="D56" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>73</v>
+      </c>
+      <c r="I56" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" t="s">
+        <v>237</v>
+      </c>
+      <c r="K56" t="s">
+        <v>238</v>
+      </c>
+      <c r="L56" t="s">
+        <v>239</v>
+      </c>
+      <c r="M56" t="s">
+        <v>30</v>
+      </c>
+      <c r="N56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O56" s="1">
+        <v>42352</v>
+      </c>
+      <c r="P56" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>33</v>
+      </c>
+      <c r="R56" s="10"/>
+      <c r="T56" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57">
+        <v>103900</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" t="s">
+        <v>247</v>
+      </c>
+      <c r="F57" t="s">
+        <v>248</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" t="s">
+        <v>73</v>
+      </c>
+      <c r="J57" t="s">
+        <v>231</v>
+      </c>
+      <c r="K57" t="s">
+        <v>232</v>
+      </c>
+      <c r="L57" t="s">
+        <v>233</v>
+      </c>
+      <c r="M57" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" s="1">
+        <v>39601</v>
+      </c>
+      <c r="P57" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>33</v>
+      </c>
+      <c r="R57" s="10"/>
+      <c r="T57" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58">
+        <v>103885</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" t="s">
+        <v>222</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" t="s">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s">
+        <v>73</v>
+      </c>
+      <c r="J58" t="s">
+        <v>240</v>
+      </c>
+      <c r="K58" t="s">
+        <v>241</v>
+      </c>
+      <c r="L58" t="s">
+        <v>242</v>
+      </c>
+      <c r="M58" t="s">
+        <v>30</v>
+      </c>
+      <c r="N58" t="s">
+        <v>31</v>
+      </c>
+      <c r="O58" s="1">
+        <v>45950</v>
+      </c>
+      <c r="P58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>33</v>
+      </c>
+      <c r="R58" s="10"/>
+      <c r="T58" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59">
+        <v>128941</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>249</v>
+      </c>
+      <c r="D59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" t="s">
+        <v>251</v>
+      </c>
+      <c r="F59" t="s">
+        <v>252</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s">
+        <v>73</v>
+      </c>
+      <c r="J59" t="s">
+        <v>253</v>
+      </c>
+      <c r="K59" t="s">
+        <v>254</v>
+      </c>
+      <c r="L59" t="s">
+        <v>255</v>
+      </c>
+      <c r="M59" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" t="s">
+        <v>31</v>
+      </c>
+      <c r="O59" s="1">
+        <v>45902</v>
+      </c>
+      <c r="P59" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>33</v>
+      </c>
+      <c r="R59" s="10"/>
+      <c r="T59" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60">
+        <v>125769</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E60" t="s">
+        <v>257</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s">
+        <v>237</v>
+      </c>
+      <c r="K60" t="s">
+        <v>238</v>
+      </c>
+      <c r="L60" t="s">
+        <v>239</v>
+      </c>
+      <c r="M60" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" t="s">
+        <v>31</v>
+      </c>
+      <c r="O60" s="1">
+        <v>44753</v>
+      </c>
+      <c r="P60" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>33</v>
+      </c>
+      <c r="R60" s="10"/>
+      <c r="T60" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61">
+        <v>118369</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" t="s">
+        <v>217</v>
+      </c>
+      <c r="D61" t="s">
+        <v>258</v>
+      </c>
+      <c r="E61" t="s">
+        <v>259</v>
+      </c>
+      <c r="F61" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s">
+        <v>73</v>
+      </c>
+      <c r="J61" t="s">
+        <v>231</v>
+      </c>
+      <c r="K61" t="s">
+        <v>232</v>
+      </c>
+      <c r="L61" t="s">
+        <v>233</v>
+      </c>
+      <c r="M61" t="s">
+        <v>24</v>
+      </c>
+      <c r="N61" t="s">
+        <v>31</v>
+      </c>
+      <c r="O61" s="1">
+        <v>42282</v>
+      </c>
+      <c r="P61" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>33</v>
+      </c>
+      <c r="R61" s="10"/>
+      <c r="T61" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62">
+        <v>120999</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" t="s">
+        <v>260</v>
+      </c>
+      <c r="D62" t="s">
+        <v>261</v>
+      </c>
+      <c r="E62" t="s">
+        <v>262</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" t="s">
+        <v>73</v>
+      </c>
+      <c r="I62" t="s">
+        <v>73</v>
+      </c>
+      <c r="J62" t="s">
+        <v>237</v>
+      </c>
+      <c r="K62" t="s">
+        <v>238</v>
+      </c>
+      <c r="L62" t="s">
+        <v>239</v>
+      </c>
+      <c r="M62" t="s">
+        <v>30</v>
+      </c>
+      <c r="N62" t="s">
+        <v>31</v>
+      </c>
+      <c r="O62" s="1">
+        <v>44403</v>
+      </c>
+      <c r="P62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>33</v>
+      </c>
+      <c r="R62" s="10"/>
+      <c r="T62" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63">
+        <v>128748</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" t="s">
+        <v>263</v>
+      </c>
+      <c r="D63" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" t="s">
+        <v>265</v>
+      </c>
+      <c r="F63" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H63" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s">
+        <v>73</v>
+      </c>
+      <c r="J63" t="s">
+        <v>234</v>
+      </c>
+      <c r="K63" t="s">
+        <v>235</v>
+      </c>
+      <c r="L63" t="s">
+        <v>236</v>
+      </c>
+      <c r="M63" t="s">
+        <v>24</v>
+      </c>
+      <c r="N63" t="s">
+        <v>31</v>
+      </c>
+      <c r="O63" s="1">
+        <v>45811</v>
+      </c>
+      <c r="P63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>33</v>
+      </c>
+      <c r="R63" s="10"/>
+      <c r="T63" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64">
+        <v>121571</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" t="s">
+        <v>266</v>
+      </c>
+      <c r="D64" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" t="s">
+        <v>268</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>73</v>
+      </c>
+      <c r="I64" t="s">
+        <v>73</v>
+      </c>
+      <c r="J64" t="s">
+        <v>237</v>
+      </c>
+      <c r="K64" t="s">
+        <v>238</v>
+      </c>
+      <c r="L64" t="s">
+        <v>239</v>
+      </c>
+      <c r="M64" t="s">
+        <v>30</v>
+      </c>
+      <c r="N64" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="1">
+        <v>43262</v>
+      </c>
+      <c r="P64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>33</v>
+      </c>
+      <c r="R64" s="10"/>
+      <c r="T64" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65">
+        <v>123862</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" t="s">
+        <v>269</v>
+      </c>
+      <c r="D65" t="s">
+        <v>270</v>
+      </c>
+      <c r="E65" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G65" t="s">
+        <v>25</v>
+      </c>
+      <c r="H65" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" t="s">
+        <v>73</v>
+      </c>
+      <c r="J65" t="s">
+        <v>266</v>
+      </c>
+      <c r="K65" t="s">
+        <v>267</v>
+      </c>
+      <c r="L65" t="s">
+        <v>268</v>
+      </c>
+      <c r="M65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N65" t="s">
+        <v>31</v>
+      </c>
+      <c r="O65" s="1">
+        <v>45706</v>
+      </c>
+      <c r="P65" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>33</v>
+      </c>
+      <c r="R65" s="10"/>
+      <c r="T65" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66">
+        <v>128655</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" t="s">
+        <v>273</v>
+      </c>
+      <c r="E66" t="s">
+        <v>274</v>
+      </c>
+      <c r="F66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G66" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" t="s">
+        <v>73</v>
+      </c>
+      <c r="I66" t="s">
+        <v>73</v>
+      </c>
+      <c r="J66" t="s">
+        <v>260</v>
+      </c>
+      <c r="K66" t="s">
+        <v>261</v>
+      </c>
+      <c r="L66" t="s">
+        <v>262</v>
+      </c>
+      <c r="M66" t="s">
+        <v>24</v>
+      </c>
+      <c r="N66" t="s">
+        <v>31</v>
+      </c>
+      <c r="O66" s="1">
+        <v>45761</v>
+      </c>
+      <c r="P66" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>33</v>
+      </c>
+      <c r="R66" s="10"/>
+      <c r="T66" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T51" xr:uid="{A937C413-DBBA-49B2-8673-0A7B750C31BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T66" xr:uid="{A937C413-DBBA-49B2-8673-0A7B750C31BC}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
